--- a/Bibsam_tidskriftslistor/bibsam_data_cellpress.xlsx
+++ b/Bibsam_tidskriftslistor/bibsam_data_cellpress.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_0BAB592D8ABFE31A5A142A9A16CF3A51EFB459EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF3AA82-1878-4DE0-887F-F8F994FC0272}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A62A8F6-17F4-49EB-8290-E05D9617D1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
+    <sheet name="Sheet21" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,22 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="136">
-  <si>
-    <t>ISSN Electronic</t>
-  </si>
-  <si>
-    <t>ISSN Print</t>
-  </si>
-  <si>
-    <t>Journal Name</t>
-  </si>
-  <si>
-    <t>JournalURL</t>
-  </si>
-  <si>
-    <t>Publishing model</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="175">
   <si>
     <t>CC License options</t>
   </si>
@@ -253,9 +238,6 @@
     <t>The American Journal of Human Genetics</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/00029297</t>
-  </si>
-  <si>
     <t>0006-3495</t>
   </si>
   <si>
@@ -280,154 +262,289 @@
     <t>One Earth</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/25903322</t>
-  </si>
-  <si>
     <t>Cell Chemical Biology</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/24519456</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/15356108</t>
-  </si>
-  <si>
     <t>3050-5623</t>
   </si>
   <si>
     <t>Cell Biomaterials</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/30505623</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/00928674</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/24054712</t>
-  </si>
-  <si>
     <t>2667-1093</t>
   </si>
   <si>
     <t>Chem Catalysis</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/26671093</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/24519294</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/19313128</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/15504131</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/09609822</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/15345807</t>
-  </si>
-  <si>
     <t>2666-9986</t>
   </si>
   <si>
     <t>Device</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/26669986</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/10747613</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/25424351</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/25902385</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/26666340</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/10972765</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/08966273</t>
-  </si>
-  <si>
     <t>2950-6360</t>
   </si>
   <si>
     <t>Newton</t>
   </si>
   <si>
-    <t>http://www.sciencedirect.com/science/journal/29506360</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/19345909</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/09692126</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/10432760</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/09680004</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/01677799</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/09628924</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/13646613</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/01689525</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/0966842X</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/01662236</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/01656147</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/24058033</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/25895974</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/01695347</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/14714906</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/14714922</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/14714914</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/13601385</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/00063495</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/16742052</t>
-  </si>
-  <si>
-    <t>http://www.sciencedirect.com/science/journal/15250016</t>
+    <t>Print ISSN</t>
+  </si>
+  <si>
+    <t>Electronic ISSN</t>
+  </si>
+  <si>
+    <t>Journal Title</t>
+  </si>
+  <si>
+    <t>Journal URL</t>
+  </si>
+  <si>
+    <t>Publishing Model</t>
+  </si>
+  <si>
+    <t>1542-0086</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/00063495</t>
+  </si>
+  <si>
+    <t>1878-3686</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/15356108</t>
+  </si>
+  <si>
+    <t>1097-4172</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/00928674</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/30505623</t>
+  </si>
+  <si>
+    <t>2451-9448</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/24519456</t>
+  </si>
+  <si>
+    <t>1934-6069</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/19313128</t>
+  </si>
+  <si>
+    <t>1932-7420</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/15504131</t>
+  </si>
+  <si>
+    <t>1875-9777</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/19345909</t>
+  </si>
+  <si>
+    <t>2405-4720</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/24054712</t>
+  </si>
+  <si>
+    <t>2451-9308</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/24519294</t>
+  </si>
+  <si>
+    <t>2667-1107</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/26671093</t>
+  </si>
+  <si>
+    <t>1879-0445</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/09609822</t>
+  </si>
+  <si>
+    <t>1878-1551</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/15345807</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/26669986</t>
+  </si>
+  <si>
+    <t>1097-4180</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/10747613</t>
+  </si>
+  <si>
+    <t>2542-4785</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/25424351</t>
+  </si>
+  <si>
+    <t>2590-2393</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/25902385</t>
+  </si>
+  <si>
+    <t>2666-6359</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/26666340</t>
+  </si>
+  <si>
+    <t>1097-4164</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/10972765</t>
+  </si>
+  <si>
+    <t>1752-9867</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/16742052</t>
+  </si>
+  <si>
+    <t>1525-0024</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/15250016</t>
+  </si>
+  <si>
+    <t>1097-4199</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/08966273</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/29506360</t>
+  </si>
+  <si>
+    <t>2590-3330</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/25903322</t>
+  </si>
+  <si>
+    <t>1878-4186</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/09692126</t>
+  </si>
+  <si>
+    <t>1537-6605</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/00029297</t>
+  </si>
+  <si>
+    <t>1362-4326</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/09680004</t>
+  </si>
+  <si>
+    <t>1879-3096</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/01677799</t>
+  </si>
+  <si>
+    <t>2405-8025</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/24058033</t>
+  </si>
+  <si>
+    <t>1879-3088</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/09628924</t>
+  </si>
+  <si>
+    <t>2589-7209</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/25895974</t>
+  </si>
+  <si>
+    <t>1879-307X</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/13646613</t>
+  </si>
+  <si>
+    <t>1872-8383</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/01695347</t>
+  </si>
+  <si>
+    <t>1879-3061</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/10432760</t>
+  </si>
+  <si>
+    <t>1362-4555</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/01689525</t>
+  </si>
+  <si>
+    <t>1471-4981</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/14714906</t>
+  </si>
+  <si>
+    <t>1878-4380</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/0966842X</t>
+  </si>
+  <si>
+    <t>1471-499X</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/14714914</t>
+  </si>
+  <si>
+    <t>1878-108X</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/01662236</t>
+  </si>
+  <si>
+    <t>1471-5007</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/14714922</t>
+  </si>
+  <si>
+    <t>1873-3735</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/01656147</t>
+  </si>
+  <si>
+    <t>1878-4372</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/journal/13601385</t>
   </si>
 </sst>
 </file>
@@ -483,19 +600,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0A8B3272-6184-4CFF-8551-F8D3151B05A8}" name="Table1" displayName="Table1" ref="A1:G43" totalsRowShown="0">
-  <autoFilter ref="A1:G43" xr:uid="{0A8B3272-6184-4CFF-8551-F8D3151B05A8}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G43">
-    <sortCondition ref="D1:D43"/>
-  </sortState>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3B164CAB-39C6-47B9-8598-6E922A405C9E}" name="Table2" displayName="Table2" ref="A1:G43" totalsRowShown="0">
+  <autoFilter ref="A1:G43" xr:uid="{3B164CAB-39C6-47B9-8598-6E922A405C9E}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{FEF91F24-558C-484F-ABFE-AA77054EEBD5}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{CFA2EF57-9E17-4396-BCE8-FDFDAA2EE9E3}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{47DB006F-E8F3-42F5-A2C5-79138B2213C1}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{6BE17262-497B-4512-9ECE-EBEB13091E42}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{A0142FDF-FDF8-478F-9179-83F8F728DBFB}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{B8DF5235-F71F-4C84-B153-3B8D37B53073}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{0EF98FFE-B0B0-4A7B-B1D8-0FA83B1BB091}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{9D189D2D-CAA6-4E8C-BEE4-5649CC1B6D1A}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{905D7F01-8F60-4784-80CC-9FAFA0927F31}" name="Print ISSN"/>
+    <tableColumn id="3" xr3:uid="{A08DD2A4-3148-4E61-8F01-CB001698E626}" name="Electronic ISSN"/>
+    <tableColumn id="4" xr3:uid="{3DAF069F-7CCF-46F6-AE3D-F669F96FE02E}" name="Journal Title"/>
+    <tableColumn id="5" xr3:uid="{AD3BF2C2-C633-4FEB-B571-6DD160F7424A}" name="Journal URL"/>
+    <tableColumn id="6" xr3:uid="{E041FBB8-7F64-41E8-9CAB-A87F5FCD2332}" name="Publishing Model"/>
+    <tableColumn id="7" xr3:uid="{8C4F2775-2753-43BD-93AD-EA3C65EAA075}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -763,880 +877,997 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424466D6-CCC2-4292-B515-707E5786FFCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC9E65B3-49E4-4897-A5FC-15B7F55014E4}">
   <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" customWidth="1"/>
     <col min="7" max="7" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" t="s">
         <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>90</v>
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F10" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>111</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>113</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>103</v>
+        <v>69</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="F15" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>122</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>126</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="F20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
         <v>74</v>
       </c>
-      <c r="B21" t="s">
-        <v>80</v>
+      <c r="C21" t="s">
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F21" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E22" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>134</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>112</v>
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>137</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>86</v>
+        <v>138</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>141</v>
       </c>
       <c r="D27" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>143</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G28" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F29" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G29" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="C30" t="s">
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E30" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="F30" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G30" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>149</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G31" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>151</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="F32" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G32" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G33" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>155</v>
       </c>
       <c r="D34" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G34" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>47</v>
+      </c>
+      <c r="C35" t="s">
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="F35" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G35" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>49</v>
+      </c>
+      <c r="C36" t="s">
+        <v>159</v>
       </c>
       <c r="D36" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="F36" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G36" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>51</v>
+      </c>
+      <c r="C37" t="s">
+        <v>161</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E37" t="s">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G37" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>58</v>
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>163</v>
       </c>
       <c r="D38" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G38" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>165</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E39" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="F39" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G39" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>167</v>
       </c>
       <c r="D40" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>124</v>
+        <v>168</v>
       </c>
       <c r="F40" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="C41" t="s">
+        <v>169</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="F41" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>66</v>
+        <v>61</v>
+      </c>
+      <c r="C42" t="s">
+        <v>171</v>
       </c>
       <c r="D42" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="F42" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="C43" t="s">
+        <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="F43" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G43" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
